--- a/AAII_Financials/Quarterly/JBIO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JBIO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="92">
   <si>
     <t>JBIO</t>
   </si>
@@ -656,56 +656,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -721,8 +722,11 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -762,8 +766,11 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -803,8 +810,11 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -844,8 +854,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,32 +874,33 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E12" s="3">
         <v>36100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>28500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13700</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,8 +916,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -943,32 +960,35 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>6200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +1004,11 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1025,8 +1048,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1039,32 +1065,33 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E17" s="3">
         <v>43400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15600</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,32 +1107,35 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-43400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-35000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-27800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-23400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15600</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1151,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,13 +1171,14 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1152,8 +1186,8 @@
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1179,32 +1213,35 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-43400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-35000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-27400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-27800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-23400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15600</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
@@ -1220,19 +1257,22 @@
       <c r="O21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1261,32 +1301,35 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16900</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,8 +1345,11 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1311,11 +1357,11 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1343,8 +1389,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1384,32 +1433,35 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-40400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16900</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1425,32 +1477,35 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-26700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24600</v>
       </c>
-      <c r="H27" s="3">
-        <v>-38200</v>
-      </c>
       <c r="I27" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="J27" s="3">
         <v>-16900</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1466,8 +1521,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1507,8 +1565,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1548,8 +1609,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1589,8 +1653,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1630,13 +1697,16 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1644,8 +1714,8 @@
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1671,32 +1741,35 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-40400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16900</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,8 +1785,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1753,32 +1829,35 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-40400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16900</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1794,37 +1873,40 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1840,8 +1922,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1857,8 +1942,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1874,29 +1960,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E41" s="3">
         <v>55100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>50100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>220900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1915,23 +2002,26 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>354000</v>
+      </c>
+      <c r="E42" s="3">
         <v>256200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>247700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>148800</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -1956,8 +2046,11 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1997,8 +2090,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2038,8 +2134,11 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2079,29 +2178,32 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>471300</v>
+      </c>
+      <c r="E46" s="3">
         <v>318500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>348800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>201400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>223000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>50700</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,8 +2222,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2161,8 +2266,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2170,7 +2278,7 @@
         <v>800</v>
       </c>
       <c r="E48" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F48" s="3">
         <v>900</v>
@@ -2179,11 +2287,11 @@
         <v>900</v>
       </c>
       <c r="H48" s="3">
+        <v>900</v>
+      </c>
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,8 +2310,11 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2225,8 +2336,8 @@
       <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2243,8 +2354,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2284,8 +2398,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2325,8 +2442,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2337,16 +2457,16 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>100</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2366,8 +2486,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2407,29 +2530,32 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>472100</v>
+      </c>
+      <c r="E54" s="3">
         <v>319400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>349800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>202500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>224000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56300</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,8 +2574,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2465,8 +2594,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2482,29 +2612,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3800</v>
+        <v>5800</v>
       </c>
       <c r="E57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2523,13 +2654,16 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
         <v>100</v>
@@ -2538,7 +2672,7 @@
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2546,8 +2680,8 @@
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2564,29 +2698,32 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,29 +2742,32 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E60" s="3">
         <v>22300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,13 +2786,16 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
         <v>700</v>
@@ -2661,14 +2804,14 @@
         <v>700</v>
       </c>
       <c r="G61" s="3">
+        <v>700</v>
+      </c>
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>123800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2687,8 +2830,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2728,8 +2874,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2769,8 +2918,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2810,8 +2962,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2851,29 +3006,32 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E66" s="3">
         <v>23000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>139800</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,8 +3050,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2909,8 +3070,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2950,8 +3112,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2991,8 +3156,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3032,8 +3200,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3073,29 +3244,32 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-270500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-214800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-174400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-142500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-117300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-85100</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,8 +3288,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3155,8 +3332,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3196,8 +3376,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3237,29 +3420,32 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>439900</v>
+      </c>
+      <c r="E76" s="3">
         <v>296500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>332500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>179300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>201600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-83500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3278,8 +3464,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3319,37 +3508,40 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3365,32 +3557,35 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-40400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16900</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3406,8 +3601,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3423,13 +3621,14 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>3</v>
@@ -3464,8 +3663,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3505,8 +3707,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3546,8 +3751,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3587,8 +3795,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3628,8 +3839,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3669,32 +3883,35 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-33600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-18800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6800</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,8 +3927,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3727,25 +3947,26 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>-100</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3768,8 +3989,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3809,8 +4033,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3850,26 +4077,29 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-98200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-148700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3891,8 +4121,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3908,8 +4141,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3949,8 +4183,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3990,8 +4227,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4031,8 +4271,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4072,32 +4315,35 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>193500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>170200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>191300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>94800</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,8 +4359,11 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4154,32 +4403,35 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-33400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>38300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-170800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>171000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>88000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
@@ -4193,6 +4445,9 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>
